--- a/output/pdf_financials_xlsx/FCR.UN.xlsx
+++ b/output/pdf_financials_xlsx/FCR.UN.xlsx
@@ -15180,7 +15180,7 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -16118,7 +16118,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
@@ -17052,7 +17052,7 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
@@ -17946,7 +17946,7 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E252" s="5" t="n">

--- a/output/pdf_financials_xlsx/FCR.UN.xlsx
+++ b/output/pdf_financials_xlsx/FCR.UN.xlsx
@@ -4235,10 +4235,10 @@
         </is>
       </c>
       <c r="B120" s="3" t="n">
-        <v>0</v>
+        <v>201.749</v>
       </c>
       <c r="C120" s="3" t="n">
-        <v>0</v>
+        <v>4.241</v>
       </c>
       <c r="D120" s="3" t="n">
         <v>0</v>
@@ -14332,7 +14332,11 @@
           <t>Issuance of common shares, net of issue costs</t>
         </is>
       </c>
-      <c r="D184" t="inlineStr"/>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E184" s="5" t="n">
         <v>201.749</v>
       </c>

--- a/output/pdf_financials_xlsx/FCR.UN.xlsx
+++ b/output/pdf_financials_xlsx/FCR.UN.xlsx
@@ -1367,28 +1367,28 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>0</v>
+        <v>3.235</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0</v>
+        <v>4.511</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0</v>
+        <v>5.589</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0</v>
+        <v>6.018</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0</v>
+        <v>5.673</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0</v>
+        <v>3.897</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0</v>
+        <v>2.567</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0</v>
+        <v>2.512</v>
       </c>
     </row>
     <row r="29">
@@ -1398,28 +1398,28 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>430.989</v>
+        <v>434.224</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>332.153</v>
+        <v>336.664</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>31.406</v>
+        <v>36.995</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>499.565</v>
+        <v>505.583</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-152.564</v>
+        <v>-146.891</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-139.16</v>
+        <v>-135.263</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>217.536</v>
+        <v>220.103</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>297.475</v>
+        <v>299.987</v>
       </c>
     </row>
     <row r="30">
@@ -3615,28 +3615,28 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>3.235</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>4.511</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>5.589</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>6.018</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>5.673</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>3.897</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>2.567</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>2.512</v>
       </c>
     </row>
     <row r="101">
@@ -4269,7 +4269,7 @@
         <v>0</v>
       </c>
       <c r="C121" s="3" t="n">
-        <v>0</v>
+        <v>-741.6</v>
       </c>
       <c r="D121" s="3" t="n">
         <v>0</v>
@@ -9828,7 +9828,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr"/>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E97" t="inlineStr">
         <is>
           <t>-</t>
@@ -9982,7 +9986,11 @@
           <t>Amortization expense</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr"/>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E100" s="5" t="n">
         <v>3.235</v>
       </c>
@@ -13350,7 +13358,11 @@
           <t>Repurchase of common shares</t>
         </is>
       </c>
-      <c r="D166" t="inlineStr"/>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E166" t="inlineStr">
         <is>
           <t>-</t>
@@ -15348,7 +15360,11 @@
           <t>Amortization expense</t>
         </is>
       </c>
-      <c r="D203" t="inlineStr"/>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E203" t="inlineStr">
         <is>
           <t>-</t>
@@ -15380,10 +15396,10 @@
         </is>
       </c>
       <c r="K203" s="5" t="n">
-        <v>-2.567</v>
+        <v>2.567</v>
       </c>
       <c r="L203" s="5" t="n">
-        <v>-2.512</v>
+        <v>2.512</v>
       </c>
     </row>
     <row r="204">
@@ -16282,27 +16298,31 @@
           <t>Amortization expense</t>
         </is>
       </c>
-      <c r="D220" t="inlineStr"/>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E220" s="5" t="n">
-        <v>-3.235</v>
+        <v>3.235</v>
       </c>
       <c r="F220" s="5" t="n">
-        <v>-4.511</v>
+        <v>4.511</v>
       </c>
       <c r="G220" s="5" t="n">
-        <v>-5.589</v>
+        <v>5.589</v>
       </c>
       <c r="H220" s="5" t="n">
-        <v>-6.018</v>
+        <v>6.018</v>
       </c>
       <c r="I220" s="5" t="n">
-        <v>-5.673</v>
+        <v>5.673</v>
       </c>
       <c r="J220" s="5" t="n">
-        <v>-3.897</v>
+        <v>3.897</v>
       </c>
       <c r="K220" s="5" t="n">
-        <v>-2.567</v>
+        <v>2.567</v>
       </c>
       <c r="L220" t="inlineStr">
         <is>
@@ -18060,7 +18080,11 @@
           <t>Share of profit from joint ventures 6</t>
         </is>
       </c>
-      <c r="D254" t="inlineStr"/>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>EarningsFromEquityInterest</t>
+        </is>
+      </c>
       <c r="E254" s="5" t="n">
         <v>30.411</v>
       </c>
